--- a/artfynd/A 29464-2024 artfynd.xlsx
+++ b/artfynd/A 29464-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112550346</v>
       </c>
       <c r="B2" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112550344</v>
+        <v>112550350</v>
       </c>
       <c r="B3" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529817</v>
+        <v>529984</v>
       </c>
       <c r="R3" t="n">
-        <v>6987562</v>
+        <v>6987604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,37 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112550343</v>
+        <v>112550347</v>
       </c>
       <c r="B4" t="n">
-        <v>78836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529844</v>
+        <v>529877</v>
       </c>
       <c r="R4" t="n">
-        <v>6987543</v>
+        <v>6987617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,15 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112550347</v>
+        <v>112550348</v>
       </c>
       <c r="B5" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1074,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529877</v>
+        <v>529965</v>
       </c>
       <c r="R5" t="n">
-        <v>6987617</v>
+        <v>6987639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112550348</v>
+        <v>112550342</v>
       </c>
       <c r="B6" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1192,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529965</v>
+        <v>529907</v>
       </c>
       <c r="R6" t="n">
-        <v>6987639</v>
+        <v>6987566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,15 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112550345</v>
+        <v>112550344</v>
       </c>
       <c r="B7" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1310,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529818</v>
+        <v>529817</v>
       </c>
       <c r="R7" t="n">
-        <v>6987583</v>
+        <v>6987562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,37 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112550350</v>
+        <v>112550343</v>
       </c>
       <c r="B8" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1428,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529984</v>
+        <v>529844</v>
       </c>
       <c r="R8" t="n">
-        <v>6987604</v>
+        <v>6987543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1438,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1496,124 +1461,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112550342</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Svarttjärn, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>529907</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6987566</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nyhem</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 29464-2024 artfynd.xlsx
+++ b/artfynd/A 29464-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550348</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550344</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,8 +1500,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>